--- a/hall/resources/sample/DailyRewards.xlsx
+++ b/hall/resources/sample/DailyRewards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="DailyRewards" sheetId="2" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>序列ID</t>
   </si>
@@ -123,34 +123,43 @@
     <t>condition</t>
   </si>
   <si>
-    <t>1990000_75000</t>
+    <t>1990000_100000</t>
   </si>
   <si>
     <t>todayDeposit(1,0)</t>
   </si>
   <si>
-    <t>1990000_150000</t>
-  </si>
-  <si>
-    <t>1990000_225000</t>
-  </si>
-  <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
-    <t>1990000_450000</t>
+    <t>1990000_200000</t>
+  </si>
+  <si>
+    <t>1990000_400000</t>
   </si>
   <si>
     <t>1990000_600000</t>
   </si>
   <si>
-    <t>1990000_900000</t>
+    <t>1990000_800000</t>
   </si>
   <si>
     <t>1990000_1500000</t>
   </si>
   <si>
-    <t>1990000_2700000</t>
+    <t>1990000_3000000</t>
+  </si>
+  <si>
+    <t>1990000_1000000</t>
+  </si>
+  <si>
+    <t>1990000_2000000</t>
+  </si>
+  <si>
+    <t>1990000_5000000</t>
+  </si>
+  <si>
+    <t>1990000_8000000</t>
+  </si>
+  <si>
+    <t>1990000_10000000</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1250,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>14</v>
@@ -1258,7 +1267,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>14</v>
@@ -1275,7 +1284,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>14</v>
@@ -1292,7 +1301,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>14</v>
@@ -1309,7 +1318,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>14</v>
@@ -1326,7 +1335,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
@@ -1343,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>14</v>
@@ -1360,7 +1369,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>14</v>
@@ -1377,7 +1386,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>14</v>
@@ -1394,7 +1403,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>14</v>
@@ -1411,7 +1420,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>

--- a/hall/resources/sample/DailyRewards.xlsx
+++ b/hall/resources/sample/DailyRewards.xlsx
@@ -126,7 +126,7 @@
     <t>1990000_100000</t>
   </si>
   <si>
-    <t>todayDeposit(1,0)</t>
+    <t>todayDeposit(0,0)</t>
   </si>
   <si>
     <t>1990000_200000</t>

--- a/hall/resources/sample/DailyRewards.xlsx
+++ b/hall/resources/sample/DailyRewards.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
@@ -129,37 +134,37 @@
     <t>todayDeposit(0,0)</t>
   </si>
   <si>
-    <t>1990000_200000</t>
-  </si>
-  <si>
-    <t>1990000_400000</t>
-  </si>
-  <si>
-    <t>1990000_600000</t>
-  </si>
-  <si>
-    <t>1990000_800000</t>
-  </si>
-  <si>
-    <t>1990000_1500000</t>
-  </si>
-  <si>
-    <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>1990000_1000000</t>
+    <t>1022502_10</t>
+  </si>
+  <si>
+    <t>1024001_5000</t>
+  </si>
+  <si>
+    <t>1990000_300000</t>
+  </si>
+  <si>
+    <t>1024013_2</t>
+  </si>
+  <si>
+    <t>1024014_2</t>
+  </si>
+  <si>
+    <t>1990000_1000000|1980000_200</t>
+  </si>
+  <si>
+    <t>1024017_3</t>
   </si>
   <si>
     <t>1990000_2000000</t>
   </si>
   <si>
-    <t>1990000_5000000</t>
-  </si>
-  <si>
-    <t>1990000_8000000</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
+    <t>1024034_2</t>
+  </si>
+  <si>
+    <t>1024035_2</t>
+  </si>
+  <si>
+    <t>1024013_3|1024014_3</t>
   </si>
 </sst>
 </file>
@@ -172,7 +177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,6 +196,25 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="0.4"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="0.4"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -668,137 +692,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -814,7 +838,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1156,7 +1186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1223,208 +1253,215 @@
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="5">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="5">
         <v>1</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="1">
+      <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="5">
         <v>1</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="5">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="1">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="5">
         <v>1</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="1">
+      <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="5">
         <v>1</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="5">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="1">
+      <c r="A10" s="5">
         <v>6</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="5">
         <v>5</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="1">
+      <c r="A11" s="5">
         <v>7</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="5">
         <v>1</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="5">
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="1">
+      <c r="A12" s="6">
         <v>101</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="6">
         <v>2</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="7">
         <v>8</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="1">
+      <c r="A13" s="6">
         <v>102</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="6">
         <v>2</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="7">
         <v>13</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="1">
+      <c r="A14" s="6">
         <v>103</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="6">
         <v>2</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="7">
         <v>18</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="1">
+      <c r="A15" s="6">
         <v>104</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="6">
         <v>2</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="7">
         <v>24</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="1">
+      <c r="A16" s="6">
         <v>105</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="6">
         <v>2</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="7">
         <v>30</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="6" t="s">
         <v>14</v>
       </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
